--- a/output/roomself_excel/3865.xlsx
+++ b/output/roomself_excel/3865.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>71810</v>
+        <v>123663</v>
       </c>
       <c r="D2" t="n">
-        <v>2196</v>
+        <v>3096</v>
       </c>
       <c r="E2" t="n">
-        <v>364</v>
+        <v>562</v>
       </c>
       <c r="F2" t="n">
-        <v>239</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16490</v>
+        <v>153479</v>
       </c>
       <c r="D3" t="n">
-        <v>1116</v>
+        <v>3159</v>
       </c>
       <c r="E3" t="n">
-        <v>104</v>
+        <v>445</v>
       </c>
       <c r="F3" t="n">
-        <v>87</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>118720</v>
+        <v>71810</v>
       </c>
       <c r="D4" t="n">
-        <v>2816</v>
+        <v>2196</v>
       </c>
       <c r="E4" t="n">
-        <v>449</v>
+        <v>364</v>
       </c>
       <c r="F4" t="n">
-        <v>310</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>354605</v>
+        <v>118720</v>
       </c>
       <c r="D5" t="n">
-        <v>6564</v>
+        <v>2816</v>
       </c>
       <c r="E5" t="n">
-        <v>811</v>
+        <v>449</v>
       </c>
       <c r="F5" t="n">
-        <v>572</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23023</v>
+        <v>77463</v>
       </c>
       <c r="D7" t="n">
-        <v>1216</v>
+        <v>3003</v>
       </c>
       <c r="E7" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -611,6 +611,50 @@
         <v>144</v>
       </c>
       <c r="F8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>16490</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1116</v>
+      </c>
+      <c r="E9" t="n">
+        <v>104</v>
+      </c>
+      <c r="F9" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>23023</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1216</v>
+      </c>
+      <c r="E10" t="n">
+        <v>161</v>
+      </c>
+      <c r="F10" t="n">
         <v>25</v>
       </c>
     </row>

--- a/output/roomself_excel/3865.xlsx
+++ b/output/roomself_excel/3865.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>3096</v>
       </c>
-      <c r="E2" t="n">
-        <v>562</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>253</v>
+        <v>537</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>229</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3159</v>
       </c>
-      <c r="E3" t="n">
-        <v>445</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>394</v>
+        <v>420</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>369</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>2196</v>
       </c>
-      <c r="E4" t="n">
-        <v>364</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>239</v>
+        <v>215</v>
+      </c>
+      <c r="G4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>334</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +609,27 @@
       <c r="D5" t="n">
         <v>2816</v>
       </c>
-      <c r="E5" t="n">
-        <v>449</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>310</v>
+        <v>424</v>
+      </c>
+      <c r="G5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>280</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +647,12 @@
       <c r="D6" t="n">
         <v>1728</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +669,12 @@
       <c r="D7" t="n">
         <v>3003</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +691,20 @@
       <c r="D8" t="n">
         <v>1016</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>144</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>25</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +721,20 @@
       <c r="D9" t="n">
         <v>1116</v>
       </c>
-      <c r="E9" t="n">
-        <v>104</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>87</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G9" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +751,20 @@
       <c r="D10" t="n">
         <v>1216</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>161</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>25</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/3865.xlsx
+++ b/output/roomself_excel/3865.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,26 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -517,6 +537,22 @@
       <c r="J2" t="n">
         <v>25</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>179</v>
+      </c>
+      <c r="N2" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -555,6 +591,22 @@
       <c r="J3" t="n">
         <v>25</v>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>242</v>
+      </c>
+      <c r="N3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -593,6 +645,22 @@
       <c r="J4" t="n">
         <v>24</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>124</v>
+      </c>
+      <c r="N4" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -630,6 +698,22 @@
       </c>
       <c r="J5" t="n">
         <v>25</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>127</v>
+      </c>
+      <c r="N5" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -653,6 +737,10 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -675,6 +763,10 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -705,6 +797,22 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>93</v>
+      </c>
+      <c r="N8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -735,6 +843,22 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>36</v>
+      </c>
+      <c r="N9" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -765,6 +889,10 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
